--- a/projetweb.xlsx
+++ b/projetweb.xlsx
@@ -2,18 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nfond\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nfond\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D904BC7-F16B-447A-A86C-C393AF8B63D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E0BCB2-DDC5-4D26-A4F7-55964DC03901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2D01C2EE-179F-4AB8-94CB-C0F2827DB6D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2D01C2EE-179F-4AB8-94CB-C0F2827DB6D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="149">
   <si>
     <t>Nom de la route</t>
   </si>
@@ -210,13 +211,306 @@
   </si>
   <si>
     <t>/user</t>
+  </si>
+  <si>
+    <t>{username, password}</t>
+  </si>
+  <si>
+    <t>Authentifie un utilisateur.</t>
+  </si>
+  <si>
+    <t>{email, username, ...}</t>
+  </si>
+  <si>
+    <t>UserDTO</t>
+  </si>
+  <si>
+    <t>Crée un nouveau compte (joueur par défaut).</t>
+  </si>
+  <si>
+    <t>UserShortDTO[]</t>
+  </si>
+  <si>
+    <t>Liste les infos basiques de tous les utilisateurs.</t>
+  </si>
+  <si>
+    <t>/users/search</t>
+  </si>
+  <si>
+    <t>Recherche un joueur spécifique.</t>
+  </si>
+  <si>
+    <t>/users/:id</t>
+  </si>
+  <si>
+    <t>Récupère les détails d'un utilisateur par son ID.</t>
+  </si>
+  <si>
+    <t>PATCH</t>
+  </si>
+  <si>
+    <t>/users/me</t>
+  </si>
+  <si>
+    <t>{firstName, lastName, ...}</t>
+  </si>
+  <si>
+    <t>Met à jour ses propres informations.</t>
+  </si>
+  <si>
+    <t>/users/:id/role</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>{role}</t>
+  </si>
+  <si>
+    <t>Modifie le rôle d'un joueur.</t>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>{message}</t>
+  </si>
+  <si>
+    <t>Désactive son propre compte (status -&gt; inactive).</t>
+  </si>
+  <si>
+    <t>Désactive le compte d'un tiers.</t>
+  </si>
+  <si>
+    <t>Query: username ou email</t>
+  </si>
+  <si>
+    <t>Path: id</t>
+  </si>
+  <si>
+    <t>/games</t>
+  </si>
+  <si>
+    <t>GameShortDTO[]</t>
+  </si>
+  <si>
+    <t>Liste des matchs et scores.</t>
+  </si>
+  <si>
+    <t>GameDTO</t>
+  </si>
+  <si>
+    <t>Crée un match (statut: "created").</t>
+  </si>
+  <si>
+    <t>/games/:id</t>
+  </si>
+  <si>
+    <t>{date, field, teams, ...}</t>
+  </si>
+  <si>
+    <t>Planifie un match (devient "scheduled").</t>
+  </si>
+  <si>
+    <t>/games/:id/status</t>
+  </si>
+  <si>
+    <t>admin, trainer et arbitre</t>
+  </si>
+  <si>
+    <t>{status}</t>
+  </si>
+  <si>
+    <t>Change l'état du match (ex: started).</t>
+  </si>
+  <si>
+    <t>/games/:id/score</t>
+  </si>
+  <si>
+    <t>{home, away}</t>
+  </si>
+  <si>
+    <t>Met à jour le score d'un match commencé.</t>
+  </si>
+  <si>
+    <t>Supprime définitivement un match.</t>
+  </si>
+  <si>
+    <t>/teams</t>
+  </si>
+  <si>
+    <t>TeamDTO[]</t>
+  </si>
+  <si>
+    <t>Liste toutes les équipes.</t>
+  </si>
+  <si>
+    <t>trainer</t>
+  </si>
+  <si>
+    <t>{name, description, sport}</t>
+  </si>
+  <si>
+    <t>TeamDTO</t>
+  </si>
+  <si>
+    <t>Un entraîneur crée son équipe.</t>
+  </si>
+  <si>
+    <t>/teams/:id/players</t>
+  </si>
+  <si>
+    <t>Un utilisateur actif rejoint l'équipe.</t>
+  </si>
+  <si>
+    <t>Un joueur quitte l'équipe.</t>
+  </si>
+  <si>
+    <t>/fields</t>
+  </si>
+  <si>
+    <t>{name, location}</t>
+  </si>
+  <si>
+    <t>FieldDTO</t>
+  </si>
+  <si>
+    <t>L'admin ajoute un nouveau terrain.</t>
+  </si>
+  <si>
+    <t>POST/auth/login</t>
+  </si>
+  <si>
+    <t>GET/users/search</t>
+  </si>
+  <si>
+    <t>GET/users/:id</t>
+  </si>
+  <si>
+    <t>PATCH/users/me</t>
+  </si>
+  <si>
+    <t>PATCH/users/:id/role</t>
+  </si>
+  <si>
+    <t>DELETE/users/me</t>
+  </si>
+  <si>
+    <t>DELETE/users/:id</t>
+  </si>
+  <si>
+    <t>GET/games</t>
+  </si>
+  <si>
+    <t>POST/games</t>
+  </si>
+  <si>
+    <t>PUT/games/:id</t>
+  </si>
+  <si>
+    <t>PATCH/games/:id/status</t>
+  </si>
+  <si>
+    <t>PATCH/games/:id/score</t>
+  </si>
+  <si>
+    <t>DELETE/games/:id</t>
+  </si>
+  <si>
+    <t>GET/teams</t>
+  </si>
+  <si>
+    <t>POST/teams</t>
+  </si>
+  <si>
+    <t>POST/teams/:id/players</t>
+  </si>
+  <si>
+    <t>DELETE/teams/:id/players</t>
+  </si>
+  <si>
+    <t>POST/fields</t>
+  </si>
+  <si>
+    <t>AuthDTO</t>
+  </si>
+  <si>
+    <t>401 (Invalid creds)</t>
+  </si>
+  <si>
+    <t>400 (Input), 409 (Conflict)</t>
+  </si>
+  <si>
+    <r>
+      <t>username</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ou </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>email</t>
+    </r>
+  </si>
+  <si>
+    <t>UserDTO[]</t>
+  </si>
+  <si>
+    <t>404 (Not found)</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>400 (Bad input)</t>
+  </si>
+  <si>
+    <t>403 (Forbidden)</t>
+  </si>
+  <si>
+    <t>403 (Admin status)</t>
+  </si>
+  <si>
+    <t>400, 422 (Started)</t>
+  </si>
+  <si>
+    <t>400 (Invalid trans.)</t>
+  </si>
+  <si>
+    <t>403 (Not started)</t>
+  </si>
+  <si>
+    <t>400 (Bad sport)</t>
+  </si>
+  <si>
+    <t>409 (Already in)</t>
+  </si>
+  <si>
+    <t>403 (Trainer leave)</t>
+  </si>
+  <si>
+    <t>FieldDTO[]</t>
+  </si>
+  <si>
+    <t>400 (Incomplete)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,16 +525,55 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -248,18 +581,155 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -292,7 +762,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CFF9FCAA-3829-4113-8164-FB17E604C418}" name="Tableau2" displayName="Tableau2" ref="A5:K30" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CFF9FCAA-3829-4113-8164-FB17E604C418}" name="Tableau2" displayName="Tableau2" ref="A5:K30" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="A5:K30" xr:uid="{CFF9FCAA-3829-4113-8164-FB17E604C418}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{296EE364-471C-43B0-850B-A7B95186C7F3}" name="Nom de la route"/>
@@ -306,6 +776,26 @@
     <tableColumn id="8" xr3:uid="{36E42D17-5322-4B02-8D21-F635D161792F}" name="Données renvoyées en cas de succès (code 200)"/>
     <tableColumn id="9" xr3:uid="{A6991DC8-201B-4F31-86E8-C07BF6DBFE25}" name="Codes d'erreurs potentiels"/>
     <tableColumn id="10" xr3:uid="{955B795F-F5DE-46CC-A9A4-DD9B08C6FF92}" name="Description"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F616BA6-6885-428A-9A67-3B6F7BF55459}" name="Tableau1" displayName="Tableau1" ref="A3:K31" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A3:K31" xr:uid="{1F616BA6-6885-428A-9A67-3B6F7BF55459}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{8E5D328D-DB6E-4428-8978-14D7BEC8107E}" name="Nom de la route"/>
+    <tableColumn id="2" xr3:uid="{E701D320-1ADF-4764-9AD5-24AD30D5152C}" name="Controller"/>
+    <tableColumn id="3" xr3:uid="{21921A4A-F0C4-4982-A403-6E722390778B}" name="Méthode HTTP"/>
+    <tableColumn id="4" xr3:uid="{BC178BE6-486A-4FC4-8780-AD6055FE0137}" name="Chemin"/>
+    <tableColumn id="5" xr3:uid="{A0572C51-BAC8-4CB6-800B-8F087CEF90E9}" name="Paramètre de chemin"/>
+    <tableColumn id="6" xr3:uid="{703CC50C-E281-4CD1-B62B-5E2E651BD721}" name="Paramètres de query"/>
+    <tableColumn id="7" xr3:uid="{368F8A77-6967-4123-99A1-8C8E38378041}" name="Qui a accès"/>
+    <tableColumn id="8" xr3:uid="{BF2E7936-06C3-4B45-B492-BBF37274C0C0}" name="Corps de la requête"/>
+    <tableColumn id="9" xr3:uid="{AE6CE435-B204-482C-9EDC-77AB6606FA8D}" name="Données renvoyées en cas de succès (code 200)"/>
+    <tableColumn id="10" xr3:uid="{B1C31DA3-73E2-4D8F-A70C-3A2999EE13CD}" name="Codes d'erreurs potentiels"/>
+    <tableColumn id="11" xr3:uid="{A9824C99-170D-4B84-AD04-2240C230561A}" name="Description"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -628,23 +1118,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6251F74D-515E-4B84-9C96-1B746F7F8599}">
+  <sheetPr codeName="Feuil1"/>
   <dimension ref="A5:K30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.36328125" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.90625" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.36328125" customWidth="1"/>
-    <col min="6" max="6" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.453125" customWidth="1"/>
-    <col min="8" max="8" width="28.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="54.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="38.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="33.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" customWidth="1"/>
+    <col min="6" max="6" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="54.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="18.75">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -679,7 +1170,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -714,7 +1205,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -749,7 +1240,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -784,7 +1275,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -819,7 +1310,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -845,7 +1336,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -871,7 +1362,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -897,7 +1388,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -923,7 +1414,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -949,7 +1440,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -972,79 +1463,1120 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
         <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662E712-5C8B-461C-9C80-338D1AA5A420}">
+  <sheetPr codeName="Feuil2"/>
+  <dimension ref="A3:K104"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.7109375" customWidth="1"/>
+    <col min="6" max="6" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="58.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="44.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:11" ht="18.75">
+      <c r="A3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="K5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="K6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="K8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="K9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="K10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="K17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="K18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="K19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="14"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="14"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="14"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="13"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="14"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="14"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="14"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="14"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="14"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="14"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="13"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="14"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="13"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="14"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="14"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="14"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="14"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="14"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="13"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="14"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="14"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="14"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="14"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="13"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="14"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I100" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="J100" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F101" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I101" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="J101" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="K101" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E102" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="F102" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="J102" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E103" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I103" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="J103" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K103" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I104" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="J104" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
